--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Auto_OV_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Auto_OV_Fiets.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.4439061019581645</v>
+        <v>0.4439031504368564</v>
       </c>
       <c r="C2">
-        <v>0.6186420519361094</v>
+        <v>0.6170674173655764</v>
       </c>
       <c r="D2">
-        <v>0.7020555702255472</v>
+        <v>0.7006890313337328</v>
       </c>
       <c r="E2">
-        <v>0.7529190144724247</v>
+        <v>0.7527649057129348</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.4583711003444285</v>
+        <v>0.4583681395719891</v>
       </c>
       <c r="C3">
-        <v>0.6301294040625675</v>
+        <v>0.6287509832441502</v>
       </c>
       <c r="D3">
-        <v>0.7081315057986718</v>
+        <v>0.706588512718861</v>
       </c>
       <c r="E3">
-        <v>0.756687626972869</v>
+        <v>0.7564955692110905</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.4210993042442046</v>
+        <v>0.4210964053546909</v>
       </c>
       <c r="C4">
-        <v>0.6016267990582209</v>
+        <v>0.6003834763058934</v>
       </c>
       <c r="D4">
-        <v>0.693547048612115</v>
+        <v>0.6921960473754905</v>
       </c>
       <c r="E4">
-        <v>0.7469217645471885</v>
+        <v>0.7467258612804342</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.4828622496992143</v>
+        <v>0.4828592662848596</v>
       </c>
       <c r="C5">
-        <v>0.6504375157112866</v>
+        <v>0.6475765481738003</v>
       </c>
       <c r="D5">
-        <v>0.7115205004370663</v>
+        <v>0.7095929480110589</v>
       </c>
       <c r="E5">
-        <v>0.7637190368229271</v>
+        <v>0.7634235085331788</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.4779840328492355</v>
+        <v>0.4779810583617347</v>
       </c>
       <c r="C6">
-        <v>0.6462407761099619</v>
+        <v>0.6434202094109371</v>
       </c>
       <c r="D6">
-        <v>0.7094697801252308</v>
+        <v>0.7075523321511903</v>
       </c>
       <c r="E6">
-        <v>0.7622870694416859</v>
+        <v>0.7619929015327521</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.4901282156980983</v>
+        <v>0.490125234680047</v>
       </c>
       <c r="C7">
-        <v>0.6545881918591552</v>
+        <v>0.6516786648199745</v>
       </c>
       <c r="D7">
-        <v>0.7199951685803621</v>
+        <v>0.7180318597321101</v>
       </c>
       <c r="E7">
-        <v>0.764221243538187</v>
+        <v>0.7639281902307521</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.4238535532033515</v>
+        <v>0.4238506133697998</v>
       </c>
       <c r="C8">
-        <v>0.5957902921233157</v>
+        <v>0.5993296787741017</v>
       </c>
       <c r="D8">
-        <v>0.6909898094845424</v>
+        <v>0.693839945186039</v>
       </c>
       <c r="E8">
-        <v>0.742960681489826</v>
+        <v>0.7433554189163866</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.4846115032126928</v>
+        <v>0.4846085133053303</v>
       </c>
       <c r="C9">
-        <v>0.6495261151428007</v>
+        <v>0.6471348910781336</v>
       </c>
       <c r="D9">
-        <v>0.7173079007704015</v>
+        <v>0.7154505454293572</v>
       </c>
       <c r="E9">
-        <v>0.7626641276885489</v>
+        <v>0.762386454026641</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.4945581757406573</v>
+        <v>0.4945552277675513</v>
       </c>
       <c r="C10">
-        <v>0.6558522342525583</v>
+        <v>0.6529559516647887</v>
       </c>
       <c r="D10">
-        <v>0.7195665583922763</v>
+        <v>0.7176657096921482</v>
       </c>
       <c r="E10">
-        <v>0.763161247005138</v>
+        <v>0.7629209925256918</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.4940951649490354</v>
+        <v>0.4942478810724729</v>
       </c>
       <c r="C11">
-        <v>0.6560788917135243</v>
+        <v>0.653316056718384</v>
       </c>
       <c r="D11">
-        <v>0.7200733864287132</v>
+        <v>0.7182092897024704</v>
       </c>
       <c r="E11">
-        <v>0.7636471422987593</v>
+        <v>0.7634211177787166</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.4846629971429635</v>
+        <v>0.4847648522690444</v>
       </c>
       <c r="C12">
-        <v>0.6462765158710355</v>
+        <v>0.6433822284364239</v>
       </c>
       <c r="D12">
-        <v>0.7133225942756337</v>
+        <v>0.711360375947285</v>
       </c>
       <c r="E12">
-        <v>0.7569472511483959</v>
+        <v>0.756658300858177</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.4935167979719632</v>
+        <v>0.4935138543068217</v>
       </c>
       <c r="C13">
-        <v>0.6546671971422592</v>
+        <v>0.6517377128140355</v>
       </c>
       <c r="D13">
-        <v>0.7186178328993582</v>
+        <v>0.7167114124602449</v>
       </c>
       <c r="E13">
-        <v>0.7622543408450436</v>
+        <v>0.7620120126676011</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Auto_OV_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Auto_OV_Fiets.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.4439031504368564</v>
+        <v>1.499967352045018</v>
       </c>
       <c r="C2">
-        <v>0.6170674173655764</v>
+        <v>0.9812219615904045</v>
       </c>
       <c r="D2">
-        <v>0.7006890313337328</v>
+        <v>0.5739776017152972</v>
       </c>
       <c r="E2">
-        <v>0.7527649057129348</v>
+        <v>0.405032595016416</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.4583681395719891</v>
+        <v>0.8688468156521109</v>
       </c>
       <c r="C3">
-        <v>0.6287509832441502</v>
+        <v>0.6455750763079641</v>
       </c>
       <c r="D3">
-        <v>0.706588512718861</v>
+        <v>0.5968860003920754</v>
       </c>
       <c r="E3">
-        <v>0.7564955692110905</v>
+        <v>0.5759226960714982</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.4210964053546909</v>
+        <v>1.027179722816074</v>
       </c>
       <c r="C4">
-        <v>0.6003834763058934</v>
+        <v>0.7786025713777481</v>
       </c>
       <c r="D4">
-        <v>0.6921960473754905</v>
+        <v>0.5628242013280013</v>
       </c>
       <c r="E4">
-        <v>0.7467258612804342</v>
+        <v>0.4703586898844337</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.4828592662848596</v>
+        <v>0.1203410864889511</v>
       </c>
       <c r="C5">
-        <v>0.6475765481738003</v>
+        <v>0.1623953572819747</v>
       </c>
       <c r="D5">
-        <v>0.7095929480110589</v>
+        <v>0.1768490164547685</v>
       </c>
       <c r="E5">
-        <v>0.7634235085331788</v>
+        <v>0.1914467622018188</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.4779810583617347</v>
+        <v>0.5262011994289484</v>
       </c>
       <c r="C6">
-        <v>0.6434202094109371</v>
+        <v>0.5573746943399905</v>
       </c>
       <c r="D6">
-        <v>0.7075523321511903</v>
+        <v>0.6676562583812192</v>
       </c>
       <c r="E6">
-        <v>0.7619929015327521</v>
+        <v>0.869216146947549</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.490125234680047</v>
+        <v>0.9312379458920891</v>
       </c>
       <c r="C7">
-        <v>0.6516786648199745</v>
+        <v>0.6190947315789758</v>
       </c>
       <c r="D7">
-        <v>0.7180318597321101</v>
+        <v>0.6201184243140953</v>
       </c>
       <c r="E7">
-        <v>0.7639281902307521</v>
+        <v>0.6047764839326789</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.4238506133697998</v>
+        <v>0.1059304751908124</v>
       </c>
       <c r="C8">
-        <v>0.5993296787741017</v>
+        <v>0.1499689205313877</v>
       </c>
       <c r="D8">
-        <v>0.693839945186039</v>
+        <v>0.17340731092867</v>
       </c>
       <c r="E8">
-        <v>0.7433554189163866</v>
+        <v>0.185782420215058</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.4846085133053303</v>
+        <v>0.8999079561421832</v>
       </c>
       <c r="C9">
-        <v>0.6471348910781336</v>
+        <v>0.7534458132581765</v>
       </c>
       <c r="D9">
-        <v>0.7154505454293572</v>
+        <v>0.6129344436238746</v>
       </c>
       <c r="E9">
-        <v>0.762386454026641</v>
+        <v>0.5316819024807189</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.4945552277675513</v>
+        <v>0.1243534821265231</v>
       </c>
       <c r="C10">
-        <v>0.6529559516647887</v>
+        <v>0.1622954099513637</v>
       </c>
       <c r="D10">
-        <v>0.7176657096921482</v>
+        <v>0.1804535165988927</v>
       </c>
       <c r="E10">
-        <v>0.7629209925256918</v>
+        <v>0.1896277611480043</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.4942478810724729</v>
+        <v>0.1275478402767672</v>
       </c>
       <c r="C11">
-        <v>0.653316056718384</v>
+        <v>0.1580603363028349</v>
       </c>
       <c r="D11">
-        <v>0.7182092897024704</v>
+        <v>0.1737603120247911</v>
       </c>
       <c r="E11">
-        <v>0.7634211177787166</v>
+        <v>0.1970119013622495</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.4847648522690444</v>
+        <v>0.4509001053814565</v>
       </c>
       <c r="C12">
-        <v>0.6433822284364239</v>
+        <v>0.5505641313837506</v>
       </c>
       <c r="D12">
-        <v>0.711360375947285</v>
+        <v>0.7191696418644836</v>
       </c>
       <c r="E12">
-        <v>0.756658300858177</v>
+        <v>0.991529432034836</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.4935138543068217</v>
+        <v>0.1240111736463295</v>
       </c>
       <c r="C13">
-        <v>0.6517377128140355</v>
+        <v>0.1604277446926857</v>
       </c>
       <c r="D13">
-        <v>0.7167114124602449</v>
+        <v>0.1800967139002668</v>
       </c>
       <c r="E13">
-        <v>0.7620120126676011</v>
+        <v>0.1914799416446793</v>
       </c>
     </row>
   </sheetData>
